--- a/src/main/resources/config.xlsx
+++ b/src/main/resources/config.xlsx
@@ -35,6 +35,7 @@
     <sheet name="Dataset Types" sheetId="18" state="hidden" r:id="rId20"/>
     <sheet name="Countries" sheetId="19" state="hidden" r:id="rId21"/>
     <sheet name="Value Sets" sheetId="15" state="hidden" r:id="rId22"/>
+    <sheet name="Organizations" sheetId="32" r:id="rId34"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1">Catalog!$A$1:$H$28</definedName>
@@ -57536,6 +57537,11 @@
       </c>
     </row>
     <row r="7" spans="1:26" ht="22.5" customHeight="1">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STAGE</t>
+        </is>
+      </c>
       <c r="A7" s="59" t="s">
         <v>2444</v>
       </c>
@@ -57551,15 +57557,14 @@
       <c r="E7" s="8" t="s">
         <v>2448</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>2428</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REQUIRED - Organization ID</t>
+        </is>
       </c>
       <c r="G7" s="14" t="str">
         <f t="shared" si="0"/>
         <v>STAGE</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>2426</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="22.5" customHeight="1">
@@ -57570,14 +57575,15 @@
       <c r="E8" s="8" t="s">
         <v>2449</v>
       </c>
-      <c r="F8" s="8" t="s">
-        <v>2446</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FROM Organizations sheet</t>
+        </is>
       </c>
       <c r="G8" s="14" t="str">
         <f>_xlfn.IFNA(INDEX(Corporate_Bodies[Uri], MATCH(H8, Corporate_Bodies[Label], 0)),"")</f>
         <v/>
       </c>
-      <c r="H8" s="8"/>
     </row>
     <row r="9" spans="1:26" ht="38.25" customHeight="1">
       <c r="A9" s="45" t="s">
@@ -57782,6 +57788,11 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="26.25" customHeight="1">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STAGE</t>
+        </is>
+      </c>
       <c r="A17" s="56" t="s">
         <v>2434</v>
       </c>
@@ -57797,13 +57808,14 @@
       <c r="E17" s="8" t="s">
         <v>2448</v>
       </c>
-      <c r="F17" s="8" t="s">
-        <v>2428</v>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REQUIRED - Organization ID</t>
+        </is>
       </c>
       <c r="G17" s="47" t="s">
         <v>2426</v>
       </c>
-      <c r="H17" s="46"/>
     </row>
     <row r="18" spans="1:8" s="5" customFormat="1" ht="26.25" customHeight="1">
       <c r="A18" s="56"/>
@@ -57813,15 +57825,14 @@
       <c r="E18" s="8" t="s">
         <v>2476</v>
       </c>
-      <c r="F18" s="13" t="s">
-        <v>2432</v>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FROM Organizations sheet</t>
+        </is>
       </c>
       <c r="G18" s="14" t="str">
         <f t="shared" ref="G18:G26" si="1">IF(H18="","",H18)</f>
         <v>https://stage-healthyageing.eu/contact</v>
-      </c>
-      <c r="H18" s="48" t="s">
-        <v>2477</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="5" customFormat="1" ht="26.25" customHeight="1">
@@ -57832,15 +57843,14 @@
       <c r="E19" s="8" t="s">
         <v>2478</v>
       </c>
-      <c r="F19" s="13" t="s">
-        <v>2432</v>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FROM Organizations sheet</t>
+        </is>
       </c>
       <c r="G19" s="14" t="str">
         <f t="shared" si="1"/>
         <v>sylvain.sebert@oulu.fi</v>
-      </c>
-      <c r="H19" s="48" t="s">
-        <v>2479</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="5" customFormat="1" ht="26.25" customHeight="1">
@@ -57851,14 +57861,15 @@
       <c r="E20" s="8" t="s">
         <v>2449</v>
       </c>
-      <c r="F20" s="8" t="s">
-        <v>2446</v>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FROM Organizations sheet</t>
+        </is>
       </c>
       <c r="G20" s="14" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H20" s="8"/>
     </row>
     <row r="21" spans="1:8" s="5" customFormat="1" ht="48" customHeight="1">
       <c r="A21" s="56"/>
@@ -57868,15 +57879,14 @@
       <c r="E21" s="8" t="s">
         <v>2480</v>
       </c>
-      <c r="F21" s="8" t="s">
-        <v>2446</v>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FROM Organizations sheet</t>
+        </is>
       </c>
       <c r="G21" s="14" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">The catalog is maintained and published by the STAGE consortium </v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>2481</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="5" customFormat="1" ht="30.75" customHeight="1">
@@ -57887,15 +57897,14 @@
       <c r="E22" s="13" t="s">
         <v>2482</v>
       </c>
-      <c r="F22" s="8" t="s">
-        <v>2446</v>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FROM Organizations sheet</t>
+        </is>
       </c>
       <c r="G22" s="14" t="str">
         <f t="shared" si="1"/>
         <v>true</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>2483</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="33" customHeight="1">
@@ -58055,8 +58064,6 @@
     <hyperlink ref="C28" r:id="rId4" location="Catalogue" display="https://healthdataeu.pages.code.europa.eu/healthdcat-ap/releases/release-5/ - Catalogue" xr:uid="{44F128B9-B51C-494F-8B1B-D19E5997EFBB}"/>
     <hyperlink ref="H12" r:id="rId5" xr:uid="{9CE524A8-D6A9-4F13-BC70-92E587998D83}"/>
     <hyperlink ref="H14" r:id="rId6" xr:uid="{532E2CA4-B4B3-44B6-A9EC-D832A6DFCEDE}"/>
-    <hyperlink ref="H19" r:id="rId7" xr:uid="{0CDCFC7B-DEE2-40EE-9456-A4CB64D52EA6}"/>
-    <hyperlink ref="H18" r:id="rId8" xr:uid="{00B0F471-AF39-4338-9B64-AD76DAB0FEB4}"/>
     <hyperlink ref="C25" r:id="rId9" location="Catalogue" display="https://healthdataeu.pages.code.europa.eu/healthdcat-ap/releases/release-5/ - Catalogue" xr:uid="{E249F9AD-4D7A-4D66-A5AE-A4C3375233D2}"/>
     <hyperlink ref="C26" r:id="rId10" location="Catalogue" display="https://healthdataeu.pages.code.europa.eu/healthdcat-ap/releases/release-5/ - Catalogue" xr:uid="{797442FA-FF85-4C42-992D-15B8BDA31E1F}"/>
   </hyperlinks>
@@ -64747,6 +64754,172 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="4" width="46" customWidth="1"/>
+    <col min="5" max="7" width="34" customWidth="1"/>
+    <col min="8" max="8" width="60" customWidth="1"/>
+    <col min="9" max="10" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organization ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Canonical IRI</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contact Page</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contact Email</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Homepage</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Description</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trusted Data Holder</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other Identifiers</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STAGE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STAGE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://stage-healthyageing.eu/contact</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sylvain.sebert@oulu.fi</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The catalog is maintained and published by the STAGE consortium</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OULU</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OULU</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">http://publications.europa.eu/resource/authority/corporate-body/EUI</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://oulu.fi</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">info@oulu.edu.fi</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The publisher provides this dataset metadata without warranties of any kind. The publisher shall not be liable for any use of the data beyond the conditions defined by the applicable access and reuse policies.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOHN_DOE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">John Doe</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">john.doe@oulu.fi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JANE_DOE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jane Doe</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E326DCC6-C92E-4984-B17B-69868B6CF2DC}">
   <dimension ref="A1:B4"/>
@@ -67741,6 +67914,11 @@
       </c>
     </row>
     <row r="11" spans="1:9" s="5" customFormat="1" ht="29.65" customHeight="1">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OULU</t>
+        </is>
+      </c>
       <c r="A11" s="56" t="s">
         <v>3160</v>
       </c>
@@ -67756,15 +67934,14 @@
       <c r="E11" s="5" t="s">
         <v>2448</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>2428</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REQUIRED - Organization ID</t>
+        </is>
       </c>
       <c r="G11" s="36" t="str">
         <f>H11</f>
         <v>OULU</v>
-      </c>
-      <c r="H11" t="s">
-        <v>3172</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="5" customFormat="1" ht="24.4" customHeight="1">
@@ -67775,15 +67952,14 @@
       <c r="E12" s="5" t="s">
         <v>2449</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>2446</v>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FROM Organizations sheet</t>
+        </is>
       </c>
       <c r="G12" s="34" t="str">
         <f>_xlfn.IFNA(INDEX(Corporate_Bodies[Uri], MATCH(H12, Corporate_Bodies[Label], 0)),"")</f>
         <v>http://publications.europa.eu/resource/authority/corporate-body/EUI</v>
-      </c>
-      <c r="H12" t="s">
-        <v>3173</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="5" customFormat="1" ht="25.9" customHeight="1">
@@ -67794,15 +67970,14 @@
       <c r="E13" s="5" t="s">
         <v>3174</v>
       </c>
-      <c r="F13" s="15" t="s">
-        <v>2432</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FROM Organizations sheet</t>
+        </is>
       </c>
       <c r="G13" s="36" t="str">
         <f>IF(H13="","",H13)</f>
         <v>https://oulu.fi</v>
-      </c>
-      <c r="H13" s="16" t="s">
-        <v>3175</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="5" customFormat="1" ht="27" customHeight="1">
@@ -67813,18 +67988,22 @@
       <c r="E14" s="5" t="s">
         <v>3176</v>
       </c>
-      <c r="F14" s="15" t="s">
-        <v>2432</v>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FROM Organizations sheet</t>
+        </is>
       </c>
       <c r="G14" s="36" t="str">
         <f>IF(H14="","",H14)</f>
         <v>info@oulu.edu.fi</v>
       </c>
-      <c r="H14" s="16" t="s">
-        <v>3177</v>
-      </c>
     </row>
     <row r="15" spans="1:9" ht="29.65" customHeight="1">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OULU</t>
+        </is>
+      </c>
       <c r="A15" s="60" t="s">
         <v>2426</v>
       </c>
@@ -67840,15 +68019,14 @@
       <c r="E15" t="s">
         <v>2448</v>
       </c>
-      <c r="F15" t="s">
-        <v>2428</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REQUIRED - Organization ID</t>
+        </is>
       </c>
       <c r="G15" s="34" t="str">
         <f>IF(H15="","",H15)</f>
         <v>OULU</v>
-      </c>
-      <c r="H15" t="s">
-        <v>3172</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="25.9" customHeight="1">
@@ -67859,15 +68037,14 @@
       <c r="E16" t="s">
         <v>2476</v>
       </c>
-      <c r="F16" s="28" t="s">
-        <v>2432</v>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FROM Organizations sheet</t>
+        </is>
       </c>
       <c r="G16" s="34" t="str">
         <f t="shared" ref="G16:G17" si="0">IF(H16="","",H16)</f>
         <v>https://oulu.fi</v>
-      </c>
-      <c r="H16" s="16" t="s">
-        <v>3175</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="30" customHeight="1">
@@ -67878,15 +68055,14 @@
       <c r="E17" t="s">
         <v>2478</v>
       </c>
-      <c r="F17" s="28" t="s">
-        <v>2432</v>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FROM Organizations sheet</t>
+        </is>
       </c>
       <c r="G17" s="34" t="str">
         <f t="shared" si="0"/>
         <v>info@oulu.edu.fi</v>
-      </c>
-      <c r="H17" s="16" t="s">
-        <v>3177</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="30.4" customHeight="1">
@@ -67897,15 +68073,14 @@
       <c r="E18" t="s">
         <v>2449</v>
       </c>
-      <c r="F18" t="s">
-        <v>2446</v>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FROM Organizations sheet</t>
+        </is>
       </c>
       <c r="G18" s="34" t="str">
         <f>_xlfn.IFNA(INDEX(Corporate_Bodies[Uri], MATCH(H18, Corporate_Bodies[Label], 0)),"")</f>
         <v>http://publications.europa.eu/resource/authority/corporate-body/EUI</v>
-      </c>
-      <c r="H18" t="s">
-        <v>3173</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="84.4" customHeight="1">
@@ -67916,15 +68091,14 @@
       <c r="E19" t="s">
         <v>3179</v>
       </c>
-      <c r="F19" t="s">
-        <v>2446</v>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FROM Organizations sheet</t>
+        </is>
       </c>
       <c r="G19" s="34" t="str">
         <f>IF(H19="","",H19)</f>
         <v>The publisher provides this dataset metadata without warranties of any kind. The publisher shall not be liable for any use of the data beyond the conditions defined by the applicable access and reuse policies.</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>3180</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="25.15" customHeight="1">
@@ -67935,16 +68109,15 @@
       <c r="E20" s="28" t="s">
         <v>2482</v>
       </c>
-      <c r="F20" t="s">
-        <v>2446</v>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FROM Organizations sheet</t>
+        </is>
       </c>
       <c r="G20" s="34" t="str">
         <f>IF(H20="","",H20)</f>
         <v>true</v>
       </c>
-      <c r="H20" t="s">
-        <v>2483</v>
-      </c>
     </row>
     <row r="21" spans="1:16" ht="25.5" customHeight="1">
       <c r="A21" s="17" t="s">
@@ -68188,6 +68361,11 @@
       <c r="I28" s="29"/>
     </row>
     <row r="29" spans="1:16" ht="29.65" customHeight="1">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOHN_DOE</t>
+        </is>
+      </c>
       <c r="A29" s="59" t="s">
         <v>2444</v>
       </c>
@@ -68203,15 +68381,14 @@
       <c r="E29" t="s">
         <v>2448</v>
       </c>
-      <c r="F29" t="s">
-        <v>2428</v>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REQUIRED - Organization ID</t>
+        </is>
       </c>
       <c r="G29" s="34" t="str">
         <f>IF(H29="","",H29)</f>
         <v>John Doe</v>
-      </c>
-      <c r="H29" t="s">
-        <v>3208</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="31.15" customHeight="1">
@@ -68222,15 +68399,14 @@
       <c r="E30" t="s">
         <v>2449</v>
       </c>
-      <c r="F30" t="s">
-        <v>2446</v>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FROM Organizations sheet</t>
+        </is>
       </c>
       <c r="G30" s="34" t="str">
         <f t="shared" ref="G30:G39" si="1">IF(H30="","",H30)</f>
         <v>john.doe@oulu.fi</v>
-      </c>
-      <c r="H30" s="16" t="s">
-        <v>3169</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="27.4" customHeight="1">
@@ -68918,6 +69094,11 @@
       </c>
     </row>
     <row r="58" spans="1:10" ht="25.5" customHeight="1">
+      <c r="H58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JANE_DOE</t>
+        </is>
+      </c>
       <c r="A58" s="59" t="s">
         <v>2444</v>
       </c>
@@ -68933,15 +69114,14 @@
       <c r="E58" t="s">
         <v>2448</v>
       </c>
-      <c r="F58" t="s">
-        <v>2428</v>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REQUIRED - Organization ID</t>
+        </is>
       </c>
       <c r="G58" s="34" t="str">
         <f>_xlfn.TEXTJOIN(",",FALSE,H58:Z58)</f>
         <v>Jane Doe,,,,,,,,,,,,,,,,,,</v>
-      </c>
-      <c r="H58" t="s">
-        <v>3269</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="23.65" customHeight="1">
@@ -69372,19 +69552,14 @@
     <hyperlink ref="H45" r:id="rId8" xr:uid="{22C4E91C-80E4-4341-AF22-087992F26B4F}"/>
     <hyperlink ref="I45" r:id="rId9" xr:uid="{922F0CEE-D5E6-4213-BB08-60E19519CC4F}"/>
     <hyperlink ref="H9" r:id="rId10" xr:uid="{4672466C-1C4D-4A40-BB41-2EFEB59DC0D7}"/>
-    <hyperlink ref="H13" r:id="rId11" xr:uid="{2F597C57-8726-4B62-B478-C4986D05D8C8}"/>
-    <hyperlink ref="H14" r:id="rId12" xr:uid="{C2086C7D-0165-4A21-88B1-B2ED144D448E}"/>
     <hyperlink ref="H28" r:id="rId13" xr:uid="{D3D7D405-FAF2-4E8D-BDE2-068A7D230232}"/>
-    <hyperlink ref="H30" r:id="rId14" xr:uid="{E12FAF52-858B-47B1-BE4B-AEF123C32CC9}"/>
     <hyperlink ref="H31" r:id="rId15" xr:uid="{C63E20A4-16D7-401B-8E8C-C9983B29A6F9}"/>
     <hyperlink ref="H33" r:id="rId16" xr:uid="{56375A8F-31F1-4A83-B6B6-259E28A4763B}"/>
     <hyperlink ref="H34" r:id="rId17" xr:uid="{7AEDC613-AB16-4280-ABFE-C060E6BA2BA0}"/>
     <hyperlink ref="H37" r:id="rId18" xr:uid="{908048EB-1C26-4735-9EAB-AF7273605690}"/>
     <hyperlink ref="H38" r:id="rId19" xr:uid="{5C9FB907-6BE2-4BBD-B2AC-FA5DB06AE827}"/>
-    <hyperlink ref="H17" r:id="rId20" xr:uid="{6BC9FDEF-5BBC-45EC-AD83-E104D62CDF0A}"/>
     <hyperlink ref="H53" r:id="rId21" xr:uid="{AA48F2B6-1E4A-4025-8E44-127A0F3E8E37}"/>
     <hyperlink ref="H57" r:id="rId22" xr:uid="{AACCF0FD-4B7E-48AA-9CFB-7988FA4B403A}"/>
-    <hyperlink ref="H16" r:id="rId23" xr:uid="{27F937F0-0DA4-4A01-9CEF-BDFF0D07C378}"/>
     <hyperlink ref="H42" r:id="rId24" xr:uid="{BFD983AB-C524-4A71-8594-585520133497}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/main/resources/config.xlsx
+++ b/src/main/resources/config.xlsx
@@ -9499,205 +9499,205 @@
     <t>party who has an interest in the resource or the use of the resource</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/ADMISSION_DISCHARGE</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/ADMISSION_DISCHARGE</t>
   </si>
   <si>
     <t>Admission Discharge</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/HOSPITAL_RECORDS</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/HOSPITAL_RECORDS</t>
   </si>
   <si>
     <t>Hospital Records</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/HEALTHCARE_VISIT</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/HEALTHCARE_VISIT</t>
   </si>
   <si>
     <t>Healthcare Visit</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/OBSERVATIONAL_DATA</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/OBSERVATIONAL_DATA</t>
   </si>
   <si>
     <t>Observational Data</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/HEALTH_SURVEY</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/HEALTH_SURVEY</t>
   </si>
   <si>
     <t>Health Survey</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/SURVEILLANCE</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/SURVEILLANCE</t>
   </si>
   <si>
     <t>Surveillance</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/NONMEDICAL_APPLICATION</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/NONMEDICAL_APPLICATION</t>
   </si>
   <si>
     <t>Nonmedical Application</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/SAMPLE_COLLECTIONS</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/SAMPLE_COLLECTIONS</t>
   </si>
   <si>
     <t>Sample Collections</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/QUALITY_REGISTRIES</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/QUALITY_REGISTRIES</t>
   </si>
   <si>
     <t>Quality Registries</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/EHEALTH_APPLICATION</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/EHEALTH_APPLICATION</t>
   </si>
   <si>
     <t>Ehealth Application</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/ROUTINE_RECORDS</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/ROUTINE_RECORDS</t>
   </si>
   <si>
     <t>Routine Records</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/HEALTH_REGISTRIES</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/HEALTH_REGISTRIES</t>
   </si>
   <si>
     <t>Health Registries</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/RESEARCH_DATABASE</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/RESEARCH_DATABASE</t>
   </si>
   <si>
     <t>Research Database</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/RESEARCH_PROJECT</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/RESEARCH_PROJECT</t>
   </si>
   <si>
     <t>Research Project</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/MUNICIPAL_REPOSITORY</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/MUNICIPAL_REPOSITORY</t>
   </si>
   <si>
     <t>Municipal Repository</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/COHORT</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/COHORT</t>
   </si>
   <si>
     <t>Cohort</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/GEOSPATIAL_MONITORING</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/GEOSPATIAL_MONITORING</t>
   </si>
   <si>
     <t>Geospatial Monitoring</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/MODELS_SIMULATIONS</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/MODELS_SIMULATIONS</t>
   </si>
   <si>
     <t>Models Simulations</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/CLINICAL_TRIAL</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/CLINICAL_TRIAL</t>
   </si>
   <si>
     <t>Clinical Trial</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/QUALITY_REGISTRY</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/QUALITY_REGISTRY</t>
   </si>
   <si>
     <t>Quality Registry</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/MEDICAL_REGISTRY</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/MEDICAL_REGISTRY</t>
   </si>
   <si>
     <t>Medical Registry</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/ADMINISTRATIVE_PROCESSES</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/ADMINISTRATIVE_PROCESSES</t>
   </si>
   <si>
     <t>Administrative Processes</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/DISEASE_MONITORING</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/DISEASE_MONITORING</t>
   </si>
   <si>
     <t>Disease Monitoring</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/PRESCRIBING_DISPENSING</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/PRESCRIBING_DISPENSING</t>
   </si>
   <si>
     <t>Prescribing Dispensing</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/AUTOMATIC_GENERATION</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/AUTOMATIC_GENERATION</t>
   </si>
   <si>
     <t>Automatic Generation</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/LABORATORY_TESTS</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/LABORATORY_TESTS</t>
   </si>
   <si>
     <t>Laboratory Tests</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/PROBABILITY_SURVEY</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/PROBABILITY_SURVEY</t>
   </si>
   <si>
     <t>Probability Survey</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/BIOBANK_COLLECTION</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/BIOBANK_COLLECTION</t>
   </si>
   <si>
     <t>Biobank Collection</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/MEASUREMENTS</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/MEASUREMENTS</t>
   </si>
   <si>
     <t>Measurements</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/PATIENT_OUTCOMES</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/PATIENT_OUTCOMES</t>
   </si>
   <si>
     <t>Patient Outcomes</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/CENSUS_DATA</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/CENSUS_DATA</t>
   </si>
   <si>
     <t>Census Data</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/MEDICAL_DEVICES</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/MEDICAL_DEVICES</t>
   </si>
   <si>
     <t>Medical Devices</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/HEALTH_SURVEILLANCE</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/HEALTH_SURVEILLANCE</t>
   </si>
   <si>
     <t>Health Surveillance</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-activity/INSURANCE_CLAIMS</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/INSURANCE_CLAIMS</t>
   </si>
   <si>
     <t>Insurance Claims</t>
@@ -23531,217 +23531,217 @@
     <t>Youth Working Party</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-theme/ENVIRONMENTAL_HEALTH</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-theme/ENVIRONMENTAL_HEALTH</t>
   </si>
   <si>
     <t>Environmental, occupational radiation health (incl. WASH urban)</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-theme/NUTRITION_SECURITY</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-theme/NUTRITION_SECURITY</t>
   </si>
   <si>
     <t>Nutrition food security</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-theme/TROPICAL_DISEASES</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-theme/TROPICAL_DISEASES</t>
   </si>
   <si>
     <t>Neglected tropical, parasitic fungal skin diseases</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-theme/RESPIRATORY_DISEASES</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-theme/RESPIRATORY_DISEASES</t>
   </si>
   <si>
     <t>Respiratory infectious diseases</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-theme/VECTOR_DISEASES</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-theme/VECTOR_DISEASES</t>
   </si>
   <si>
     <t>Vector-borne zoonotic viral diseases</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-theme/EMERGENCY_SETTINGS</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-theme/EMERGENCY_SETTINGS</t>
   </si>
   <si>
     <t>Emergencies, disasters, travel humanitarian settings</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-theme/REPRODUCTIVE_HEALTH</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-theme/REPRODUCTIVE_HEALTH</t>
   </si>
   <si>
     <t>Sexual reproductive health and rights</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-theme/BLOOD_INFECTIONS</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-theme/BLOOD_INFECTIONS</t>
   </si>
   <si>
     <t>Blood-borne sexually transmitted infections</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-theme/HEALTH_PRODUCTS</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-theme/HEALTH_PRODUCTS</t>
   </si>
   <si>
     <t>Health products, technologies, data research</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-theme/LIFECOURSE_HEALTH</t>
-  </si>
-  <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-theme/ENTERIC_INFECTIONS</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-theme/LIFECOURSE_HEALTH</t>
+  </si>
+  <si>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-theme/ENTERIC_INFECTIONS</t>
   </si>
   <si>
     <t>Enteric, water- food-borne infections</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-theme/NONCOMMUNICABLE_DISEASES</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-theme/NONCOMMUNICABLE_DISEASES</t>
   </si>
   <si>
     <t>Noncommunicable diseases ? metabolic cardiopulmonary</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-theme/HEALTH_SYSTEMS</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-theme/HEALTH_SYSTEMS</t>
   </si>
   <si>
     <t>Health systems, quality, care models determinants</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-theme/CLIMATE_HEALTH</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-theme/CLIMATE_HEALTH</t>
   </si>
   <si>
     <t>Climate planetary health</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-theme/ANTIMICROBIAL_CONTROL</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-theme/ANTIMICROBIAL_CONTROL</t>
   </si>
   <si>
     <t>Antimicrobial resistance infection control</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-theme/MENTAL_HEALTH</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-theme/MENTAL_HEALTH</t>
   </si>
   <si>
     <t>Mental, neurological substance use</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-theme/SENSORY_HEALTH</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-theme/SENSORY_HEALTH</t>
   </si>
   <si>
     <t>Oral, eye sensory health</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-theme/IMMUNIZATION_DISEASES</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-theme/IMMUNIZATION_DISEASES</t>
   </si>
   <si>
     <t>Immunization vaccine-preventable diseases</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-theme/INJURY_PREVENTION</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-theme/INJURY_PREVENTION</t>
   </si>
   <si>
     <t>Injuries, envenoming drowning</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/health-theme/CANCER_DISEASE</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-theme/CANCER_DISEASE</t>
   </si>
   <si>
     <t>Cancer</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/healthcategories/PGEH</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/healthcategories/PGEH</t>
   </si>
   <si>
     <t>Personal electronic health data automatically generated through medical devices</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/healthcategories/RQSH</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/healthcategories/RQSH</t>
   </si>
   <si>
     <t>Data from research cohorts, questionnaires and surveys related to health, after the first publication of the related results</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/healthcategories/NRPE</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/healthcategories/NRPE</t>
   </si>
   <si>
     <t>Aggregated data on healthcare needs, resources allocated to healthcare, the provision of and access to healthcare, healthcare expenditure and financing</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/healthcategories/RMMD</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/healthcategories/RMMD</t>
   </si>
   <si>
     <t>Data from registries for medicinal products and medical devices</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/healthcategories/DIOH</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/healthcategories/DIOH</t>
   </si>
   <si>
     <t>Data on factors impacting on health, including socio-economic, environmental and behavioural determinants of health</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/healthcategories/EMRD</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/healthcategories/EMRD</t>
   </si>
   <si>
     <t>Other health data from medical devices</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/healthcategories/EHCT</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/healthcategories/EHCT</t>
   </si>
   <si>
     <t>Data from clinical trials, clinical studies, clinical investigations and performance studies subject to Regulation (EU) No 536/2014, Regulation (EU) 2024/1938 of the European Parliament and of the Council34, Regulation (EU) 2017/745 and Regulation (EU) 2017/746</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/healthcategories/EHRS</t>
-  </si>
-  <si>
-    <t>http://13.81.34.152:1101/resource/authority/healthcategories/MRMR</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/healthcategories/EHRS</t>
+  </si>
+  <si>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/healthcategories/MRMR</t>
   </si>
   <si>
     <t>Data from medical registries and mortality registries</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/healthcategories/HRAD</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/healthcategories/HRAD</t>
   </si>
   <si>
     <t>Healthcare-related administrative data, including on dispensations, reimbursement claims and reimbursements</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/healthcategories/IDHP</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/healthcategories/IDHP</t>
   </si>
   <si>
     <t>Data on professional status, and on the specialisation and institution of health professionals involved in the treatment of a natural person</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/healthcategories/HGPD</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/healthcategories/HGPD</t>
   </si>
   <si>
     <t>Human genetic, epigenomic and genomic data</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/healthcategories/RPDG</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/healthcategories/RPDG</t>
   </si>
   <si>
     <t>Data on pathogens that impact human health</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/healthcategories/PHDR</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/healthcategories/PHDR</t>
   </si>
   <si>
     <t>Data from population-based health data registries such as public health registries</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/healthcategories/EINS</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/healthcategories/EINS</t>
   </si>
   <si>
     <t>Health data from biobanks and associated databases</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/healthcategories/HPML</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/healthcategories/HPML</t>
   </si>
   <si>
     <t>Other human molecular data such as proteomic, transcriptomic, metabolomic, lipidomic and other omic data</t>
   </si>
   <si>
-    <t>http://13.81.34.152:1101/resource/authority/healthcategories/WELA</t>
+    <t>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/healthcategories/WELA</t>
   </si>
   <si>
     <t>Data from wellness applications</t>
@@ -67631,7 +67631,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B89FB9D3-3C26-4805-A4F2-39333E3C7845}">
-  <dimension ref="A1:P75"/>
+  <dimension ref="A1:P76"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17.42578125" customWidth="1"/>
@@ -68218,7 +68218,7 @@
       </c>
       <c r="G23" s="34" t="str">
         <f>INDEX(Health_Categories[Uri], MATCH(H23, Health_Categories[Label], 0))</f>
-        <v>http://13.81.34.152:1101/resource/authority/healthcategories/EHRS</v>
+        <v>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/healthcategories/EHRS</v>
       </c>
       <c r="H23" t="s">
         <v>3195</v>
@@ -68326,7 +68326,7 @@
       </c>
       <c r="G27" s="34" t="str">
         <f>INDEX(Health_Themes[Uri], MATCH(H27, Health_Themes[Label], 0))</f>
-        <v>http://13.81.34.152:1101/resource/authority/health-theme/LIFECOURSE_HEALTH</v>
+        <v>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-theme/LIFECOURSE_HEALTH</v>
       </c>
       <c r="H27" t="s">
         <v>3203</v>
@@ -69285,7 +69285,7 @@
       </c>
       <c r="G65" s="34" t="str" cm="1">
         <f t="array" aca="1" ref="G65" ca="1">INDIRECT("Helpers!A1")</f>
-        <v>http://13.81.34.152:1101/resource/authority/health-activity/EHEALTH_APPLICATION,http://13.81.34.152:1101/resource/authority/health-activity/OBSERVATIONAL_DATA,http://13.81.34.152:1101/resource/authority/health-activity/SURVEILLANCE</v>
+        <v>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/EHEALTH_APPLICATION,https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/OBSERVATIONAL_DATA,https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/SURVEILLANCE</v>
       </c>
       <c r="H65" t="s">
         <v>3093</v>
@@ -69445,6 +69445,43 @@
     <row r="75" spans="1:10">
       <c r="B75" s="41"/>
       <c r="E75" s="1"/>
+    </row>
+    <row r="76">
+      <c r="H76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Release 7. Whether the dataset holds structured data that can be described variable by variable. Leave empty to derive it: true when a data dictionary / extracted columns exist. When true, the CSVW variables description is mandatory.</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REQUIRED</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">structured data</t>
+        </is>
+      </c>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEALTHDCAT-AP</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H26" xr:uid="{B89FB9D3-3C26-4805-A4F2-39333E3C7845}"/>
@@ -69582,19 +69619,19 @@
     <row r="1" spans="1:27">
       <c r="A1" t="str">
         <f>_xlfn.TEXTJOIN(",", TRUE, H1:AA1)</f>
-        <v>http://13.81.34.152:1101/resource/authority/health-activity/EHEALTH_APPLICATION,http://13.81.34.152:1101/resource/authority/health-activity/OBSERVATIONAL_DATA,http://13.81.34.152:1101/resource/authority/health-activity/SURVEILLANCE</v>
+        <v>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/EHEALTH_APPLICATION,https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/OBSERVATIONAL_DATA,https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/SURVEILLANCE</v>
       </c>
       <c r="H1" t="str">
         <f>IFERROR(INDEX(Health_Activities[Uri], MATCH(Dataset!H65, Health_Activities[Label], 0)),"")</f>
-        <v>http://13.81.34.152:1101/resource/authority/health-activity/EHEALTH_APPLICATION</v>
+        <v>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/EHEALTH_APPLICATION</v>
       </c>
       <c r="I1" t="str">
         <f>IFERROR(INDEX(Health_Activities[Uri], MATCH(Dataset!I65, Health_Activities[Label], 0)),"")</f>
-        <v>http://13.81.34.152:1101/resource/authority/health-activity/OBSERVATIONAL_DATA</v>
+        <v>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/OBSERVATIONAL_DATA</v>
       </c>
       <c r="J1" t="str">
         <f>IFERROR(INDEX(Health_Activities[Uri], MATCH(Dataset!J65, Health_Activities[Label], 0)),"")</f>
-        <v>http://13.81.34.152:1101/resource/authority/health-activity/SURVEILLANCE</v>
+        <v>https://hdeu-dcat.acceptance.data.health.europa.eu/resource/authority/health-activity/SURVEILLANCE</v>
       </c>
       <c r="K1" t="str">
         <f>IFERROR(INDEX(Health_Activities[Uri], MATCH(Dataset!K65, Health_Activities[Label], 0)), "")</f>
